--- a/results/Int Task Remove ACC 0.5/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_6_permute.xlsx
@@ -440,337 +440,337 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6170029917637103</v>
+        <v>0.6391188004338653</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6170029917637103</v>
+        <v>0.6394322800576897</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.620512056450171</v>
+        <v>0.6394322800576897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6230401563822305</v>
+        <v>0.6328086820744485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6191973491304814</v>
+        <v>0.6356299986888685</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6172962084460708</v>
+        <v>0.6327985506037165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6229692360871069</v>
+        <v>0.6378648819385675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6314737118132949</v>
+        <v>0.6378648819385675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5813968318295053</v>
+        <v>0.6391188004338653</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5867462483759849</v>
+        <v>0.6384918411862164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5848653706330381</v>
+        <v>0.6400592393053387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5912160148753829</v>
+        <v>0.6429109503319547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6009946720383327</v>
+        <v>0.6416367688951929</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5914889686162794</v>
+        <v>0.6416367688951929</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.578757285719394</v>
+        <v>0.5866449336686652</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5794146393792389</v>
+        <v>0.5812549912392577</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.479836585336782</v>
+        <v>0.5746009988438204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4659624301226504</v>
+        <v>0.5454569293300118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4622209375782209</v>
+        <v>0.5188105653360668</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4678939652192569</v>
+        <v>0.5178701264645935</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4750128133306316</v>
+        <v>0.5157466893929461</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4712105319618103</v>
+        <v>0.5040061027211938</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4712105319618103</v>
+        <v>0.5068578137478098</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4699464819957805</v>
+        <v>0.5068578137478098</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4824755354780266</v>
+        <v>0.4884834976220843</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4852765891509827</v>
+        <v>0.4881497550567958</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4871675983646614</v>
+        <v>0.4494898506502021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4871675983646614</v>
+        <v>0.4494898506502021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4871675983646614</v>
+        <v>0.4526347783591785</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4875013409299498</v>
+        <v>0.4570944133878446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4875114724006818</v>
+        <v>0.4279300809325721</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4890991334612679</v>
+        <v>0.4250783699059561</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4881789575312586</v>
+        <v>0.4250783699059561</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4888059167789074</v>
+        <v>0.4250783699059561</v>
       </c>
     </row>
     <row r="36">
@@ -780,237 +780,237 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4875418668128777</v>
+        <v>0.4250783699059561</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4903530519565658</v>
+        <v>0.4250783699059561</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4852968520924467</v>
+        <v>0.4247648902821317</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4859238113400956</v>
+        <v>0.4247648902821317</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4866014279414044</v>
+        <v>0.4247648902821317</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4841138538922727</v>
+        <v>0.4614420062695925</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4803115725234514</v>
+        <v>0.4554858934169279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4913745425938949</v>
+        <v>0.4558095045114843</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4957835202689012</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4919913703708118</v>
+        <v>0.4429568399346818</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4919913703708118</v>
+        <v>0.4426433603108573</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4831126261964075</v>
+        <v>0.4461017676436583</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4890991334612679</v>
+        <v>0.450227660107036</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4871777298353934</v>
+        <v>0.450227660107036</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4789968652037618</v>
+        <v>0.4514815786023338</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.484012539184953</v>
+        <v>0.4514815786023338</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.484012539184953</v>
+        <v>0.4520984063792508</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4880877742946709</v>
+        <v>0.4514613156608699</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4824755354780266</v>
+        <v>0.4536151471447131</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4784306947805047</v>
+        <v>0.4495601749764592</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4905658128419371</v>
+        <v>0.470856526455058</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4862277554620547</v>
+        <v>0.470856526455058</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.479987961428895</v>
+        <v>0.4714733542319749</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4774699929675674</v>
+        <v>0.4714733542319749</v>
       </c>
     </row>
     <row r="60">
@@ -1020,87 +1020,87 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4774699929675674</v>
+        <v>0.4714733542319749</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4803318354649153</v>
+        <v>0.4705329153605016</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4765498170375579</v>
+        <v>0.4849529780564263</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4774497300261035</v>
+        <v>0.4852664576802508</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4821316614420063</v>
+        <v>0.4833855799373041</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4821417929127382</v>
+        <v>0.4858934169278997</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4808878744174404</v>
+        <v>0.4855799373040752</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4818283132889138</v>
+        <v>0.4852765891509827</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4818283132889138</v>
+        <v>0.4859846001644874</v>
       </c>
     </row>
     <row r="69">
@@ -1110,217 +1110,217 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4903125260736379</v>
+        <v>0.4903834463687617</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4928406260056975</v>
+        <v>0.4862676853761159</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4899889149790815</v>
+        <v>0.4884417798014232</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4815452280772852</v>
+        <v>0.4879566611440218</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4778037355328558</v>
+        <v>0.4882802722385783</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4778037355328558</v>
+        <v>0.5373475809623705</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4775003873797632</v>
+        <v>0.5389960308473485</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4775003873797632</v>
+        <v>0.5695561223881664</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4762464688844654</v>
+        <v>0.558817359381146</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.485640726128467</v>
+        <v>0.5446905133675817</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4875216038714137</v>
+        <v>0.54292048583382</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5000405258829279</v>
+        <v>0.5672205204000144</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5000405258829279</v>
+        <v>0.5672205204000144</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5000405258829279</v>
+        <v>0.5663510018236648</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5016079240020501</v>
+        <v>0.5663510018236648</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5012843129074938</v>
+        <v>0.5600003575813199</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5019112721551426</v>
+        <v>0.5372975195775773</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5003540055067524</v>
+        <v>0.5376109992014018</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5003540055067524</v>
+        <v>0.5504642597470708</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5003540055067524</v>
+        <v>0.5466536348141173</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5009809647544012</v>
+        <v>0.4771183713362814</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5016079240020501</v>
+        <v>0.4966661501603156</v>
       </c>
     </row>
   </sheetData>
